--- a/slide_classification/SurGen_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.9060402684563759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8774193548387097</v>
+        <v>0.8588957055214724</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8838709677419355</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8954507857733665</v>
+        <v>0.8719907367512053</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7120567375886525</v>
+        <v>0.5991071428571428</v>
       </c>
       <c r="C3" t="n">
-        <v>0.652482269503546</v>
+        <v>0.692063492063492</v>
       </c>
       <c r="D3" t="n">
-        <v>0.575</v>
+        <v>0.5328828828828829</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5785714285714286</v>
+        <v>0.5558752997601919</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6295276089159068</v>
+        <v>0.5949822043909274</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7253521126760563</v>
+        <v>0.586044226044226</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6840277777777778</v>
+        <v>0.7050339366515836</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5356125356125356</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5935314685314685</v>
+        <v>0.5722222222222222</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6473945064129923</v>
+        <v>0.5997282301326419</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9073672806067171</v>
+        <v>0.8370440370440372</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8999732905982905</v>
+        <v>0.9027718728172733</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8662365591397848</v>
+        <v>0.8517644591264223</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8705729754116852</v>
+        <v>0.8719336219336219</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8860375264391195</v>
+        <v>0.8658784977303386</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8288416075650118</v>
+        <v>0.6892857142857143</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8089834515366431</v>
+        <v>0.7439153439153439</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8347619047619048</v>
+        <v>0.6463963963963963</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7390476190476191</v>
+        <v>0.8067146282973621</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8029086457277947</v>
+        <v>0.7215780207237041</v>
       </c>
     </row>
     <row r="7">
@@ -578,31 +579,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[135   6]
- [  8   7]]</t>
+          <t>[[124, 16], [11, 5]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[137   4]
- [ 10   5]]</t>
+          <t>[[129, 6], [8, 6]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[133   7]
- [ 12   3]]</t>
+          <t>[[138, 10], [13, 2]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[134   6]
- [ 12   3]]</t>
+          <t>[[136, 3], [13, 2]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[135, 6], [10, 4]]</t>
+          <t>[[132, 9], [11, 4]]</t>
         </is>
       </c>
     </row>
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8141025641025641</v>
+        <v>0.7243589743589743</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.7315436241610739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8451612903225807</v>
+        <v>0.7116564417177914</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7225806451612903</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7925765095119934</v>
+        <v>0.7237079418776418</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6886524822695035</v>
+        <v>0.6526785714285714</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7936170212765958</v>
+        <v>0.6597883597883598</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7654761904761904</v>
+        <v>0.6015765765765766</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6976190476190476</v>
+        <v>0.581294964028777</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7363411854103343</v>
+        <v>0.6238346179555712</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6234706616729089</v>
+        <v>0.5618836130886291</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6458204334365325</v>
+        <v>0.5602125147579693</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6821599453178401</v>
+        <v>0.5260748530776369</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5716856243172033</v>
+        <v>0.5284339457567804</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6307841661861212</v>
+        <v>0.5441512316702539</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8398636319984635</v>
+        <v>0.7739567162204483</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8273636580138128</v>
+        <v>0.7831271839813634</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8657200185213768</v>
+        <v>0.7680586892456815</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7767060330727563</v>
+        <v>0.7749940348365545</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8274133354016024</v>
+        <v>0.7750341560710119</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7711583924349882</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8066193853427897</v>
+        <v>0.6947089947089947</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8361904761904762</v>
+        <v>0.6148648648648649</v>
       </c>
       <c r="E12" t="n">
-        <v>0.738095238095238</v>
+        <v>0.6556354916067146</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7880158730158731</v>
+        <v>0.6484451949380007</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[119  22]
- [  7   8]]</t>
+          <t>[[104, 36], [7, 9]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[111  30]
- [  3  12]]</t>
+          <t>[[101, 34], [6, 8]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[121  19]
- [  5  10]]</t>
+          <t>[[109, 39], [8, 7]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[102  38]
- [  5  10]]</t>
+          <t>[[106, 33], [9, 6]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[113, 27], [5, 10]]</t>
+          <t>[[105, 36], [8, 8]]</t>
         </is>
       </c>
     </row>
@@ -759,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.8782051282051282</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.912751677852349</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.8895705521472392</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.9025974025974026</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8954818031430936</v>
+        <v>0.8957811902005297</v>
       </c>
     </row>
     <row r="15">
@@ -781,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5297872340425532</v>
+        <v>0.4892857142857143</v>
       </c>
       <c r="C15" t="n">
-        <v>0.526241134751773</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5226190476190476</v>
+        <v>0.4898648648648649</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4928571428571429</v>
+        <v>0.5594724220623501</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5178761398176291</v>
+        <v>0.5185843217318038</v>
       </c>
     </row>
     <row r="16">
@@ -803,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5333998005982054</v>
+        <v>0.4675767918088737</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5283446712018141</v>
+        <v>0.5436984687868081</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5234219569542413</v>
+        <v>0.4707792207792208</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4709897610921502</v>
+        <v>0.5793116008013113</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5140390474616028</v>
+        <v>0.5153415205440535</v>
       </c>
     </row>
     <row r="17">
@@ -825,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8692000920315974</v>
+        <v>0.8392403955543887</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8653410081981511</v>
+        <v>0.8769480083161398</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8606467949054544</v>
+        <v>0.8549119592064377</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8508202135858196</v>
+        <v>0.8762555965251285</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8615020271802556</v>
+        <v>0.8618389899005237</v>
       </c>
     </row>
     <row r="18">
@@ -847,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7127659574468084</v>
+        <v>0.6013392857142857</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6056737588652481</v>
+        <v>0.5624338624338624</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.6216216216216215</v>
       </c>
       <c r="E18" t="n">
-        <v>0.635</v>
+        <v>0.5175059952038369</v>
       </c>
       <c r="F18" t="n">
-        <v>0.657109929078014</v>
+        <v>0.5757251912434016</v>
       </c>
     </row>
     <row r="19">
@@ -870,26 +863,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 14   1]]</t>
+          <t>[[137, 3], [16, 0]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[139   2]
- [ 14   1]]</t>
+          <t>[[135, 0], [13, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[137   3]
- [ 14   1]]</t>
+          <t>[[145, 3], [15, 0]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 15   0]]</t>
+          <t>[[137, 2], [13, 2]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -905,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.6987179487179487</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6346153846153846</v>
+        <v>0.6510067114093959</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6838709677419355</v>
+        <v>0.5705521472392638</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6302626137303556</v>
+        <v>0.6407834875559378</v>
       </c>
     </row>
     <row r="21">
@@ -927,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5716312056737589</v>
+        <v>0.6107142857142858</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5297872340425531</v>
+        <v>0.5513227513227513</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6464285714285714</v>
+        <v>0.5538288288288289</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5702380952380952</v>
+        <v>0.6237410071942446</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5795212765957447</v>
+        <v>0.5849017182650277</v>
       </c>
     </row>
     <row r="22">
@@ -949,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4700854700854701</v>
+        <v>0.5326066169439663</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4696725711218465</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5335053129414655</v>
+        <v>0.4471899224806202</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4689434129089302</v>
+        <v>0.506266394637132</v>
       </c>
       <c r="F22" t="n">
-        <v>0.485551691764428</v>
+        <v>0.4921754557376518</v>
       </c>
     </row>
     <row r="23">
@@ -971,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6840894148586457</v>
+        <v>0.7540883926426094</v>
       </c>
       <c r="C23" t="n">
-        <v>0.708555266526281</v>
+        <v>0.7223154362416108</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7470928907830422</v>
+        <v>0.6602701288819138</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6816976127320955</v>
+        <v>0.7153682808010992</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7053587962250161</v>
+        <v>0.7130105596418083</v>
       </c>
     </row>
     <row r="24">
@@ -993,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6288416075650118</v>
+        <v>0.7160714285714287</v>
       </c>
       <c r="C24" t="n">
-        <v>0.633096926713948</v>
+        <v>0.673015873015873</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7628571428571428</v>
+        <v>0.6229729729729729</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.6153477218225419</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6603655859506924</v>
+        <v>0.6568519990957042</v>
       </c>
     </row>
     <row r="25">
@@ -1016,31 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[86 55]
- [ 7  8]]</t>
+          <t>[[101, 39], [8, 8]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[93 48]
- [ 9  6]]</t>
+          <t>[[91, 44], [8, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[97 43]
- [ 6  9]]</t>
+          <t>[[85, 63], [7, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[85 55]
- [ 7  8]]</t>
+          <t>[[90, 49], [6, 9]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[90, 50], [7, 8]]</t>
+          <t>[[92, 49], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.8993288590604027</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8967741935483871</v>
+        <v>0.8834355828220859</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8967741935483871</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9035153019023987</v>
+        <v>0.8908709306504423</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4928571428571429</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4962962962962963</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5261904761904762</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4964285714285714</v>
+        <v>0.4964028776978417</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5223214285714286</v>
+        <v>0.4930107008344419</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5388513513513513</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5388513513513513</v>
+        <v>0.4734982332155477</v>
       </c>
       <c r="D28" t="n">
-        <v>0.528158295281583</v>
+        <v>0.4690553745928339</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4727891156462585</v>
+        <v>0.4726027397260274</v>
       </c>
       <c r="F28" t="n">
-        <v>0.519662528407636</v>
+        <v>0.4711360256591124</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8731159043659045</v>
+        <v>0.8424908424908426</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8731159043659045</v>
+        <v>0.858016932672469</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8644866696126086</v>
+        <v>0.851781539137907</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8540706605222734</v>
+        <v>0.8531400106742572</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8661972847166728</v>
+        <v>0.851357331243869</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7976359338061465</v>
+        <v>0.7723214285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>0.755082742316785</v>
+        <v>0.6804232804232805</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8771428571428571</v>
+        <v>0.7283783783783784</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6819047619047619</v>
+        <v>0.7122302158273381</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7779415737926376</v>
+        <v>0.7233383258001065</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[141   0]
- [ 14   1]]</t>
+          <t>[[138, 2], [16, 0]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[141   0]
- [ 14   1]]</t>
+          <t>[[134, 1], [14, 0]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 14   1]]</t>
+          <t>[[144, 4], [15, 0]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[139   1]
- [ 15   0]]</t>
+          <t>[[138, 1], [15, 0]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[140, 1], [14, 1]]</t>
+          <t>[[138, 2], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8719907367512053</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.03139820404338939</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5949822043909274</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.06088404399978339</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5997282301326419</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.06352941552601624</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8658784977303386</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.02463948996633832</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7215780207237041</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06008799307702054</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[132, 9], [11, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>622</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7237079418776418</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.007412288970934184</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6238346179555712</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0332779497789898</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5441512316702539</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01692771916635527</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7750341560710119</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.005369281249246714</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6484451949380007</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03047394252820181</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[105, 36], [8, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>622</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8957811902005297</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01305706880271193</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5185843217318038</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03020135765033573</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5153415205440535</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04786323106842657</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8618389899005237</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01577023465828904</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5757251912434016</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03977655831655976</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[138, 2], [14, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>622</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6407834875559378</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04581936627965066</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5849017182650277</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.03266439377087235</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4921754557376518</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03141606939625124</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7130105596418083</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.03376788777219952</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6568519990957042</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04073881776184005</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[92, 49], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>622</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8908709306504423</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.006952279013935409</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4930107008344419</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.004027746091860884</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4711360256591124</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.00194401861450036</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.851357331243869</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.005619671082106327</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7233383258001065</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03312792520653762</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[138, 2], [15, 0]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/SurGen_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
